--- a/artfynd/A 62754-2025 artfynd.xlsx
+++ b/artfynd/A 62754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305118</v>
       </c>
       <c r="B2" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305119</v>
       </c>
       <c r="B3" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62754-2025 artfynd.xlsx
+++ b/artfynd/A 62754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305118</v>
       </c>
       <c r="B2" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305119</v>
       </c>
       <c r="B3" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62754-2025 artfynd.xlsx
+++ b/artfynd/A 62754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305118</v>
       </c>
       <c r="B2" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305119</v>
       </c>
       <c r="B3" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62754-2025 artfynd.xlsx
+++ b/artfynd/A 62754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305118</v>
       </c>
       <c r="B2" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305119</v>
       </c>
       <c r="B3" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62754-2025 artfynd.xlsx
+++ b/artfynd/A 62754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305118</v>
       </c>
       <c r="B2" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305119</v>
       </c>
       <c r="B3" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62754-2025 artfynd.xlsx
+++ b/artfynd/A 62754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305118</v>
       </c>
       <c r="B2" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305119</v>
       </c>
       <c r="B3" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62754-2025 artfynd.xlsx
+++ b/artfynd/A 62754-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137305118</v>
+        <v>137512085</v>
       </c>
       <c r="B2" t="n">
-        <v>87616</v>
+        <v>87394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>248947</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kappelshamn, Gtl</t>
+          <t>Flenvike, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>722968</v>
+        <v>722953</v>
       </c>
       <c r="R2" t="n">
-        <v>6419463</v>
+        <v>6419482</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137305118</t>
+          <t>https://artportalen.se/Sighting/137512085</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137305119</v>
+        <v>137512258</v>
       </c>
       <c r="B3" t="n">
-        <v>87509</v>
+        <v>75611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>248956</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kappelshamn, Gtl</t>
+          <t>Flenvike, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>722988</v>
+        <v>722860</v>
       </c>
       <c r="R3" t="n">
-        <v>6419470</v>
+        <v>6419448</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,25 +861,453 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137512258</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137305118</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87616</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kappelshamn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>722968</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6419463</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137305118</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137511846</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87617</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flenvike, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>722921</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6419467</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137511846</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137305119</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87509</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kappelshamn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>722988</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6419470</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137305119</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137512381</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87510</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flenvike, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>722888</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6419450</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137512381</t>
         </is>
       </c>
     </row>
@@ -907,6 +1315,10 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62754-2025 artfynd.xlsx
+++ b/artfynd/A 62754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137512085</v>
       </c>
       <c r="B2" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137512258</v>
       </c>
       <c r="B3" t="n">
-        <v>75611</v>
+        <v>75614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137305118</v>
       </c>
       <c r="B4" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137511846</v>
       </c>
       <c r="B5" t="n">
-        <v>87617</v>
+        <v>87620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137305119</v>
       </c>
       <c r="B6" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137512381</v>
       </c>
       <c r="B7" t="n">
-        <v>87510</v>
+        <v>87513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
